--- a/data/trans_orig/P79A10_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79A10_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>21727</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34145</t>
+          <t>41345</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28420</t>
+          <t>33976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38082</t>
+          <t>45974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>16359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36979</t>
+          <t>42408</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>45711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>64045</t>
+          <t>72865</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53095</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70431</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10865</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23807</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42832</t>
+          <t>49112</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42832</t>
+          <t>49112</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42832</t>
+          <t>49112</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>76902</t>
+          <t>86279</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>76902</t>
+          <t>86279</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>76902</t>
+          <t>86279</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28051</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15327</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>22244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37754</t>
+          <t>42552</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45851</t>
+          <t>50555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>13695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>32805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>56864</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56864</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56864</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43995</t>
+          <t>50794</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38622</t>
+          <t>46255</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46109</t>
+          <t>53809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>40455</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>35696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37319</t>
+          <t>43585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>78805</t>
+          <t>91249</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73392</t>
+          <t>84481</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82655</t>
+          <t>95735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>54646</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>54646</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>54646</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>47049</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>47049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>47049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>86882</t>
+          <t>101695</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86882</t>
+          <t>101695</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>86882</t>
+          <t>101695</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>111250</t>
+          <t>127650</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99232</t>
+          <t>111307</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120296</t>
+          <t>138862</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>103497</t>
+          <t>120360</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>108837</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111253</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>214748</t>
+          <t>248009</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196269</t>
+          <t>229941</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>227843</t>
+          <t>261933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>29957</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>46300</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>36114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>54549</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
